--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5617"/>
+  <dimension ref="A1:B5620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56522,6 +56522,36 @@
         <v>0.997</v>
       </c>
     </row>
+    <row r="5618">
+      <c r="A5618" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B5618" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5619">
+      <c r="A5619" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B5619" t="n">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="5620">
+      <c r="A5620" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B5620" t="n">
+        <v>1.001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5620"/>
+  <dimension ref="A1:B5624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56552,6 +56552,46 @@
         <v>1.001</v>
       </c>
     </row>
+    <row r="5621">
+      <c r="A5621" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B5621" t="n">
+        <v>1.006</v>
+      </c>
+    </row>
+    <row r="5622">
+      <c r="A5622" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B5622" t="n">
+        <v>1.003</v>
+      </c>
+    </row>
+    <row r="5623">
+      <c r="A5623" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B5623" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="5624">
+      <c r="A5624" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B5624" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5624"/>
+  <dimension ref="A1:B5627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56592,6 +56592,36 @@
         <v>0.995</v>
       </c>
     </row>
+    <row r="5625">
+      <c r="A5625" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B5625" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="5626">
+      <c r="A5626" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B5626" t="n">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="5627">
+      <c r="A5627" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B5627" t="n">
+        <v>0.993</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5627"/>
+  <dimension ref="A1:B5629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56622,6 +56622,26 @@
         <v>0.993</v>
       </c>
     </row>
+    <row r="5628">
+      <c r="A5628" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B5628" t="n">
+        <v>0.993</v>
+      </c>
+    </row>
+    <row r="5629">
+      <c r="A5629" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5629" t="n">
+        <v>1.003</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5629"/>
+  <dimension ref="A1:B5633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56642,6 +56642,46 @@
         <v>1.003</v>
       </c>
     </row>
+    <row r="5630">
+      <c r="A5630" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B5630" t="n">
+        <v>1.006</v>
+      </c>
+    </row>
+    <row r="5631">
+      <c r="A5631" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B5631" t="n">
+        <v>1.005</v>
+      </c>
+    </row>
+    <row r="5632">
+      <c r="A5632" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B5632" t="n">
+        <v>1.002</v>
+      </c>
+    </row>
+    <row r="5633">
+      <c r="A5633" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B5633" t="n">
+        <v>1.002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5633"/>
+  <dimension ref="A1:B5637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56682,6 +56682,46 @@
         <v>1.002</v>
       </c>
     </row>
+    <row r="5634">
+      <c r="A5634" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B5634" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5635">
+      <c r="A5635" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B5635" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="5636">
+      <c r="A5636" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B5636" t="n">
+        <v>0.989</v>
+      </c>
+    </row>
+    <row r="5637">
+      <c r="A5637" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B5637" t="n">
+        <v>0.992</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5637"/>
+  <dimension ref="A1:B5639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56722,6 +56722,24 @@
         <v>0.992</v>
       </c>
     </row>
+    <row r="5638">
+      <c r="A5638" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B5638" t="n">
+        <v>0.993</v>
+      </c>
+    </row>
+    <row r="5639">
+      <c r="A5639" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B5639" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5639"/>
+  <dimension ref="A1:B5641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56738,7 +56738,29 @@
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="B5639" t="inlineStr"/>
+      <c r="B5639" t="n">
+        <v>0.948</v>
+      </c>
+    </row>
+    <row r="5640">
+      <c r="A5640" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B5640" t="n">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="5641">
+      <c r="A5641" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B5641" t="n">
+        <v>0.994</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5641"/>
+  <dimension ref="A1:B5648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56762,6 +56762,74 @@
         <v>0.994</v>
       </c>
     </row>
+    <row r="5642">
+      <c r="A5642" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B5642" t="n">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="5643">
+      <c r="A5643" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B5643" t="n">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="5644">
+      <c r="A5644" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B5644" t="n">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="5645">
+      <c r="A5645" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B5645" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="5646">
+      <c r="A5646" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B5646" t="n">
+        <v>0.988</v>
+      </c>
+    </row>
+    <row r="5647">
+      <c r="A5647" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B5647" t="n">
+        <v>0.986</v>
+      </c>
+    </row>
+    <row r="5648">
+      <c r="A5648" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B5648" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5648"/>
+  <dimension ref="A1:B5650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56828,7 +56828,29 @@
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="B5648" t="inlineStr"/>
+      <c r="B5648" t="n">
+        <v>0.989</v>
+      </c>
+    </row>
+    <row r="5649">
+      <c r="A5649" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B5649" t="n">
+        <v>0.989</v>
+      </c>
+    </row>
+    <row r="5650">
+      <c r="A5650" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B5650" t="n">
+        <v>0.979</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5650"/>
+  <dimension ref="A1:B5651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56852,6 +56852,16 @@
         <v>0.979</v>
       </c>
     </row>
+    <row r="5651">
+      <c r="A5651" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B5651" t="n">
+        <v>0.979</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5651"/>
+  <dimension ref="A1:B5652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56862,6 +56862,16 @@
         <v>0.979</v>
       </c>
     </row>
+    <row r="5652">
+      <c r="A5652" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B5652" t="n">
+        <v>0.965</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5652"/>
+  <dimension ref="A1:B5656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56872,6 +56872,46 @@
         <v>0.965</v>
       </c>
     </row>
+    <row r="5653">
+      <c r="A5653" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B5653" t="n">
+        <v>0.988</v>
+      </c>
+    </row>
+    <row r="5654">
+      <c r="A5654" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B5654" t="n">
+        <v>0.982</v>
+      </c>
+    </row>
+    <row r="5655">
+      <c r="A5655" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B5655" t="n">
+        <v>1.001</v>
+      </c>
+    </row>
+    <row r="5656">
+      <c r="A5656" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B5656" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5656"/>
+  <dimension ref="A1:B5657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56912,6 +56912,16 @@
         <v>0.99</v>
       </c>
     </row>
+    <row r="5657">
+      <c r="A5657" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B5657" t="n">
+        <v>0.986</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5657"/>
+  <dimension ref="A1:B5662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56922,6 +56922,56 @@
         <v>0.986</v>
       </c>
     </row>
+    <row r="5658">
+      <c r="A5658" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B5658" t="n">
+        <v>0.984</v>
+      </c>
+    </row>
+    <row r="5659">
+      <c r="A5659" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B5659" t="n">
+        <v>0.981</v>
+      </c>
+    </row>
+    <row r="5660">
+      <c r="A5660" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B5660" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="5661">
+      <c r="A5661" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B5661" t="n">
+        <v>1.001</v>
+      </c>
+    </row>
+    <row r="5662">
+      <c r="A5662" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B5662" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5662"/>
+  <dimension ref="A1:B5665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56972,6 +56972,36 @@
         <v>0.998</v>
       </c>
     </row>
+    <row r="5663">
+      <c r="A5663" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B5663" t="n">
+        <v>0.988</v>
+      </c>
+    </row>
+    <row r="5664">
+      <c r="A5664" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B5664" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="5665">
+      <c r="A5665" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B5665" t="n">
+        <v>0.988</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5665"/>
+  <dimension ref="A1:B5666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57002,6 +57002,16 @@
         <v>0.988</v>
       </c>
     </row>
+    <row r="5666">
+      <c r="A5666" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B5666" t="n">
+        <v>0.991</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5666"/>
+  <dimension ref="A1:B5669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57012,6 +57012,36 @@
         <v>0.991</v>
       </c>
     </row>
+    <row r="5667">
+      <c r="A5667" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B5667" t="n">
+        <v>0.985</v>
+      </c>
+    </row>
+    <row r="5668">
+      <c r="A5668" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B5668" t="n">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="5669">
+      <c r="A5669" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B5669" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5669"/>
+  <dimension ref="A1:B5671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57042,6 +57042,26 @@
         <v>0.997</v>
       </c>
     </row>
+    <row r="5670">
+      <c r="A5670" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B5670" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="5671">
+      <c r="A5671" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B5671" t="n">
+        <v>0.979</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5671"/>
+  <dimension ref="A1:B5672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57062,6 +57062,16 @@
         <v>0.979</v>
       </c>
     </row>
+    <row r="5672">
+      <c r="A5672" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B5672" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5672"/>
+  <dimension ref="A1:B5674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57072,6 +57072,26 @@
         <v>0.997</v>
       </c>
     </row>
+    <row r="5673">
+      <c r="A5673" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B5673" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="5674">
+      <c r="A5674" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B5674" t="n">
+        <v>0.991</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5674"/>
+  <dimension ref="A1:B5677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57092,6 +57092,36 @@
         <v>0.991</v>
       </c>
     </row>
+    <row r="5675">
+      <c r="A5675" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B5675" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="5676">
+      <c r="A5676" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B5676" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="5677">
+      <c r="A5677" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B5677" t="n">
+        <v>0.999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5677"/>
+  <dimension ref="A1:B5680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57122,6 +57122,36 @@
         <v>0.999</v>
       </c>
     </row>
+    <row r="5678">
+      <c r="A5678" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B5678" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="5679">
+      <c r="A5679" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B5679" t="n">
+        <v>1.002</v>
+      </c>
+    </row>
+    <row r="5680">
+      <c r="A5680" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B5680" t="n">
+        <v>0.999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5680"/>
+  <dimension ref="A1:B5682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57152,6 +57152,26 @@
         <v>0.999</v>
       </c>
     </row>
+    <row r="5681">
+      <c r="A5681" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B5681" t="n">
+        <v>0.988</v>
+      </c>
+    </row>
+    <row r="5682">
+      <c r="A5682" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B5682" t="n">
+        <v>0.993</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5682"/>
+  <dimension ref="A1:B5689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57172,6 +57172,76 @@
         <v>0.993</v>
       </c>
     </row>
+    <row r="5683">
+      <c r="A5683" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B5683" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="5684">
+      <c r="A5684" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B5684" t="n">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="5685">
+      <c r="A5685" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B5685" t="n">
+        <v>1.001</v>
+      </c>
+    </row>
+    <row r="5686">
+      <c r="A5686" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B5686" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="5687">
+      <c r="A5687" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B5687" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="5688">
+      <c r="A5688" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B5688" t="n">
+        <v>1.003</v>
+      </c>
+    </row>
+    <row r="5689">
+      <c r="A5689" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B5689" t="n">
+        <v>0.991</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_sopr_sth.xlsx
+++ b/data_cripto/btc_sopr_sth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5689"/>
+  <dimension ref="A1:B5696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57242,6 +57242,74 @@
         <v>0.991</v>
       </c>
     </row>
+    <row r="5690">
+      <c r="A5690" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B5690" t="n">
+        <v>1.003</v>
+      </c>
+    </row>
+    <row r="5691">
+      <c r="A5691" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B5691" t="n">
+        <v>1.006</v>
+      </c>
+    </row>
+    <row r="5692">
+      <c r="A5692" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B5692" t="n">
+        <v>1.002</v>
+      </c>
+    </row>
+    <row r="5693">
+      <c r="A5693" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B5693" t="n">
+        <v>0.994</v>
+      </c>
+    </row>
+    <row r="5694">
+      <c r="A5694" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B5694" t="n">
+        <v>0.993</v>
+      </c>
+    </row>
+    <row r="5695">
+      <c r="A5695" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B5695" t="n">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="5696">
+      <c r="A5696" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B5696" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
